--- a/public/manifest_generated.xlsx
+++ b/public/manifest_generated.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
   <si>
     <t>BTN GATEWAY</t>
   </si>
@@ -122,381 +122,381 @@
     <t>TOTAL</t>
   </si>
   <si>
+    <t>LE21585223</t>
+  </si>
+  <si>
+    <t>EZ</t>
+  </si>
+  <si>
+    <t>LE21643149</t>
+  </si>
+  <si>
+    <t>E58239887</t>
+  </si>
+  <si>
+    <t>LE21767076</t>
+  </si>
+  <si>
+    <t>LE21695404</t>
+  </si>
+  <si>
+    <t>LE21895451</t>
+  </si>
+  <si>
+    <t>LE21662996</t>
+  </si>
+  <si>
+    <t>LE21924940</t>
+  </si>
+  <si>
+    <t>LE21583393</t>
+  </si>
+  <si>
+    <t>LE21998645</t>
+  </si>
+  <si>
+    <t>LE21772780</t>
+  </si>
+  <si>
+    <t>LE21648541</t>
+  </si>
+  <si>
+    <t>LE20811545</t>
+  </si>
+  <si>
+    <t>F06911597</t>
+  </si>
+  <si>
+    <t>LE21955895</t>
+  </si>
+  <si>
+    <t>LE21647176</t>
+  </si>
+  <si>
+    <t>LE21647659</t>
+  </si>
+  <si>
+    <t>LE21986062</t>
+  </si>
+  <si>
+    <t>LE21754420</t>
+  </si>
+  <si>
+    <t>F10291368</t>
+  </si>
+  <si>
+    <t>LE21571910</t>
+  </si>
+  <si>
+    <t>F06911566</t>
+  </si>
+  <si>
+    <t>LE21573663</t>
+  </si>
+  <si>
     <t>LE21897986</t>
   </si>
   <si>
-    <t>EZ</t>
+    <t>LE21732627</t>
+  </si>
+  <si>
+    <t>LE21589886</t>
+  </si>
+  <si>
+    <t>LE21923220</t>
+  </si>
+  <si>
+    <t>LE21659521</t>
+  </si>
+  <si>
+    <t>LE20851374</t>
+  </si>
+  <si>
+    <t>LE21669151</t>
+  </si>
+  <si>
+    <t>LE21549556</t>
+  </si>
+  <si>
+    <t>LE21652580</t>
+  </si>
+  <si>
+    <t>LE21547955</t>
+  </si>
+  <si>
+    <t>LE21735033</t>
+  </si>
+  <si>
+    <t>LE21767911</t>
+  </si>
+  <si>
+    <t>LE21633679</t>
+  </si>
+  <si>
+    <t>LE21774440</t>
+  </si>
+  <si>
+    <t>LE21672104</t>
+  </si>
+  <si>
+    <t>LE21673945</t>
+  </si>
+  <si>
+    <t>LE21749912</t>
+  </si>
+  <si>
+    <t>LE21693977</t>
+  </si>
+  <si>
+    <t>LE21766935</t>
+  </si>
+  <si>
+    <t>LE21666060</t>
+  </si>
+  <si>
+    <t>LE21461966</t>
+  </si>
+  <si>
+    <t>LE22034463</t>
+  </si>
+  <si>
+    <t>LE19400403</t>
+  </si>
+  <si>
+    <t>LE21365607</t>
+  </si>
+  <si>
+    <t>LE21687330</t>
+  </si>
+  <si>
+    <t>LE21545695</t>
+  </si>
+  <si>
+    <t>LE21764062</t>
+  </si>
+  <si>
+    <t>LE21657092</t>
+  </si>
+  <si>
+    <t>LE21901893</t>
+  </si>
+  <si>
+    <t>F07078177</t>
+  </si>
+  <si>
+    <t>LE21624725</t>
+  </si>
+  <si>
+    <t>LE21554075</t>
+  </si>
+  <si>
+    <t>E58239886</t>
+  </si>
+  <si>
+    <t>LE21737109</t>
+  </si>
+  <si>
+    <t>LE21530251</t>
   </si>
   <si>
     <t>LE21670560</t>
   </si>
   <si>
-    <t>LE21365607</t>
-  </si>
-  <si>
-    <t>LE21669151</t>
+    <t>LE21669020</t>
+  </si>
+  <si>
+    <t>LE21618454</t>
+  </si>
+  <si>
+    <t>LE21718366</t>
+  </si>
+  <si>
+    <t>LE21638270</t>
+  </si>
+  <si>
+    <t>LE21568144</t>
+  </si>
+  <si>
+    <t>LE21997445</t>
+  </si>
+  <si>
+    <t>LE21586072</t>
+  </si>
+  <si>
+    <t>LE21609351</t>
+  </si>
+  <si>
+    <t>F06950533</t>
+  </si>
+  <si>
+    <t>LE21210682</t>
+  </si>
+  <si>
+    <t>LE21790005</t>
+  </si>
+  <si>
+    <t>LE21709548</t>
+  </si>
+  <si>
+    <t>LE21572200</t>
+  </si>
+  <si>
+    <t>LE21734658</t>
+  </si>
+  <si>
+    <t>LE21642830</t>
+  </si>
+  <si>
+    <t>LE21649918</t>
+  </si>
+  <si>
+    <t>LE21563739</t>
+  </si>
+  <si>
+    <t>LE21995147</t>
+  </si>
+  <si>
+    <t>LE21686094</t>
+  </si>
+  <si>
+    <t>LE21570475</t>
+  </si>
+  <si>
+    <t>LE20821676</t>
+  </si>
+  <si>
+    <t>LE21700219</t>
+  </si>
+  <si>
+    <t>LE21769697</t>
+  </si>
+  <si>
+    <t>LE21701655</t>
+  </si>
+  <si>
+    <t>LE21572305</t>
+  </si>
+  <si>
+    <t>LE21580852</t>
+  </si>
+  <si>
+    <t>LE21947492</t>
+  </si>
+  <si>
+    <t>LE21618282</t>
+  </si>
+  <si>
+    <t>LE21446642</t>
+  </si>
+  <si>
+    <t>LE21673217</t>
+  </si>
+  <si>
+    <t>LE21688757</t>
+  </si>
+  <si>
+    <t>LE21656989</t>
+  </si>
+  <si>
+    <t>LE21585387</t>
+  </si>
+  <si>
+    <t>LE21893303</t>
+  </si>
+  <si>
+    <t>LE21707779</t>
+  </si>
+  <si>
+    <t>LE21661245</t>
+  </si>
+  <si>
+    <t>LE21674683</t>
+  </si>
+  <si>
+    <t>LE21579239</t>
+  </si>
+  <si>
+    <t>LE21720855</t>
+  </si>
+  <si>
+    <t>LE21586571</t>
+  </si>
+  <si>
+    <t>LE21848415</t>
+  </si>
+  <si>
+    <t>LE21625517</t>
+  </si>
+  <si>
+    <t>LE22004503</t>
+  </si>
+  <si>
+    <t>LE21946085</t>
+  </si>
+  <si>
+    <t>LE21637424</t>
+  </si>
+  <si>
+    <t>LE21660884</t>
+  </si>
+  <si>
+    <t>LE21886290</t>
+  </si>
+  <si>
+    <t>LE21979354</t>
+  </si>
+  <si>
+    <t>LE21655828</t>
+  </si>
+  <si>
+    <t>LE21635568</t>
   </si>
   <si>
     <t>LE21662488</t>
   </si>
   <si>
-    <t>LE21530251</t>
+    <t>LE21755772</t>
+  </si>
+  <si>
+    <t>F10291369</t>
+  </si>
+  <si>
+    <t>LE21867064</t>
+  </si>
+  <si>
+    <t>LE21666695</t>
   </si>
   <si>
     <t>LE21553982</t>
   </si>
   <si>
+    <t>LE21640971</t>
+  </si>
+  <si>
+    <t>LE21846605</t>
+  </si>
+  <si>
+    <t>LE21952018</t>
+  </si>
+  <si>
+    <t>LE20503355</t>
+  </si>
+  <si>
     <t>LE21990298</t>
   </si>
   <si>
-    <t>LE21662996</t>
-  </si>
-  <si>
-    <t>LE21749912</t>
-  </si>
-  <si>
-    <t>LE21657092</t>
-  </si>
-  <si>
-    <t>LE21686094</t>
-  </si>
-  <si>
-    <t>LE21895451</t>
-  </si>
-  <si>
-    <t>LE21586072</t>
-  </si>
-  <si>
-    <t>LE21764062</t>
-  </si>
-  <si>
-    <t>LE21867064</t>
-  </si>
-  <si>
-    <t>LE21774440</t>
-  </si>
-  <si>
-    <t>LE21674683</t>
-  </si>
-  <si>
-    <t>LE21579239</t>
-  </si>
-  <si>
-    <t>LE21618282</t>
-  </si>
-  <si>
-    <t>LE21946085</t>
-  </si>
-  <si>
-    <t>F07078177</t>
-  </si>
-  <si>
-    <t>LE21720855</t>
-  </si>
-  <si>
-    <t>LE21635568</t>
-  </si>
-  <si>
-    <t>LE21672104</t>
-  </si>
-  <si>
-    <t>LE21955895</t>
-  </si>
-  <si>
-    <t>LE21687330</t>
-  </si>
-  <si>
-    <t>LE21754420</t>
-  </si>
-  <si>
-    <t>LE21673945</t>
-  </si>
-  <si>
-    <t>LE21661245</t>
-  </si>
-  <si>
-    <t>LE21647176</t>
-  </si>
-  <si>
-    <t>LE21693977</t>
-  </si>
-  <si>
-    <t>LE21656989</t>
-  </si>
-  <si>
-    <t>LE21655828</t>
-  </si>
-  <si>
-    <t>LE21589886</t>
-  </si>
-  <si>
     <t>LE21758090</t>
   </si>
   <si>
-    <t>LE21737109</t>
-  </si>
-  <si>
-    <t>LE21580852</t>
-  </si>
-  <si>
-    <t>LE21571910</t>
-  </si>
-  <si>
-    <t>LE21986062</t>
-  </si>
-  <si>
-    <t>LE21767911</t>
-  </si>
-  <si>
-    <t>LE21649918</t>
+    <t>LE21666944</t>
   </si>
   <si>
     <t>LE21955834</t>
   </si>
   <si>
-    <t>E58239886</t>
-  </si>
-  <si>
-    <t>LE21718366</t>
-  </si>
-  <si>
-    <t>LE21554075</t>
-  </si>
-  <si>
-    <t>LE21563739</t>
-  </si>
-  <si>
-    <t>LE21640971</t>
-  </si>
-  <si>
-    <t>LE21568144</t>
-  </si>
-  <si>
-    <t>LE21769697</t>
-  </si>
-  <si>
-    <t>F06911566</t>
-  </si>
-  <si>
-    <t>LE21998645</t>
-  </si>
-  <si>
-    <t>LE21886290</t>
-  </si>
-  <si>
-    <t>LE20821676</t>
-  </si>
-  <si>
-    <t>LE19400403</t>
-  </si>
-  <si>
-    <t>LE21642830</t>
-  </si>
-  <si>
-    <t>LE22004503</t>
-  </si>
-  <si>
-    <t>LE21609351</t>
-  </si>
-  <si>
-    <t>LE21846605</t>
-  </si>
-  <si>
-    <t>LE21735033</t>
-  </si>
-  <si>
-    <t>LE21848415</t>
-  </si>
-  <si>
-    <t>LE21700219</t>
-  </si>
-  <si>
-    <t>F10291368</t>
-  </si>
-  <si>
-    <t>LE21709548</t>
-  </si>
-  <si>
-    <t>LE21995147</t>
-  </si>
-  <si>
-    <t>LE21647659</t>
-  </si>
-  <si>
-    <t>F06950533</t>
-  </si>
-  <si>
-    <t>LE21583393</t>
-  </si>
-  <si>
-    <t>LE21633679</t>
-  </si>
-  <si>
-    <t>LE21666944</t>
-  </si>
-  <si>
-    <t>LE21660884</t>
-  </si>
-  <si>
-    <t>LE21772780</t>
-  </si>
-  <si>
-    <t>LE20503355</t>
-  </si>
-  <si>
-    <t>LE21997445</t>
-  </si>
-  <si>
-    <t>LE21638270</t>
-  </si>
-  <si>
-    <t>LE21734658</t>
-  </si>
-  <si>
-    <t>LE21732627</t>
-  </si>
-  <si>
-    <t>LE21446642</t>
-  </si>
-  <si>
-    <t>LE21210682</t>
-  </si>
-  <si>
-    <t>LE21572200</t>
-  </si>
-  <si>
-    <t>LE21461966</t>
-  </si>
-  <si>
-    <t>LE21573663</t>
-  </si>
-  <si>
-    <t>LE21923220</t>
-  </si>
-  <si>
-    <t>LE21695404</t>
-  </si>
-  <si>
-    <t>LE21652580</t>
-  </si>
-  <si>
-    <t>LE21637424</t>
-  </si>
-  <si>
-    <t>LE22034463</t>
-  </si>
-  <si>
-    <t>LE21618454</t>
-  </si>
-  <si>
-    <t>LE21755772</t>
-  </si>
-  <si>
-    <t>LE21947492</t>
-  </si>
-  <si>
-    <t>LE21901893</t>
-  </si>
-  <si>
-    <t>LE21545695</t>
-  </si>
-  <si>
-    <t>LE21643149</t>
-  </si>
-  <si>
-    <t>LE20811545</t>
-  </si>
-  <si>
-    <t>LE21659521</t>
-  </si>
-  <si>
-    <t>LE21952018</t>
-  </si>
-  <si>
-    <t>LE21669020</t>
-  </si>
-  <si>
-    <t>LE21924940</t>
-  </si>
-  <si>
-    <t>LE21547955</t>
-  </si>
-  <si>
-    <t>LE21572305</t>
-  </si>
-  <si>
-    <t>LE21767076</t>
-  </si>
-  <si>
-    <t>LE21673217</t>
-  </si>
-  <si>
-    <t>LE20851374</t>
-  </si>
-  <si>
-    <t>LE21625517</t>
-  </si>
-  <si>
-    <t>F10291369</t>
-  </si>
-  <si>
-    <t>LE21666695</t>
-  </si>
-  <si>
-    <t>LE21586571</t>
-  </si>
-  <si>
-    <t>E58239887</t>
-  </si>
-  <si>
-    <t>LE21790005</t>
-  </si>
-  <si>
-    <t>LE21624725</t>
-  </si>
-  <si>
     <t>LE21693743</t>
   </si>
   <si>
-    <t>LE21766935</t>
-  </si>
-  <si>
-    <t>LE21688757</t>
-  </si>
-  <si>
-    <t>LE21585223</t>
-  </si>
-  <si>
-    <t>LE21701655</t>
-  </si>
-  <si>
-    <t>LE21666060</t>
-  </si>
-  <si>
-    <t>LE21707779</t>
-  </si>
-  <si>
-    <t>LE21549556</t>
-  </si>
-  <si>
-    <t>LE21585387</t>
-  </si>
-  <si>
-    <t>LE21570475</t>
-  </si>
-  <si>
-    <t>LE21648541</t>
-  </si>
-  <si>
-    <t>LE21893303</t>
-  </si>
-  <si>
-    <t>LE21979354</t>
-  </si>
-  <si>
-    <t>F06911597</t>
-  </si>
-  <si>
     <t>JAT GATEWAY</t>
   </si>
   <si>
@@ -521,436 +521,19 @@
     <t>2026-04-13</t>
   </si>
   <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>538</t>
+    <t>0</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>117</t>
-  </si>
-  <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>139</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>124</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>154</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>194</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>127</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>192</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>149</t>
-  </si>
-  <si>
-    <t>10717</t>
-  </si>
-  <si>
-    <t>dfdf</t>
   </si>
 </sst>
 </file>
@@ -2404,7 +1987,7 @@
         <v>27</v>
       </c>
       <c r="E11" s="38">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F11" s="38" t="s">
         <v>28</v>
@@ -2420,7 +2003,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="38">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>28</v>
@@ -2436,7 +2019,7 @@
         <v>30</v>
       </c>
       <c r="E13" s="38">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>28</v>
@@ -2452,7 +2035,7 @@
         <v>31</v>
       </c>
       <c r="E14" s="38">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>28</v>
@@ -2468,7 +2051,7 @@
         <v>32</v>
       </c>
       <c r="E15" s="38">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>28</v>
@@ -2484,7 +2067,7 @@
         <v>33</v>
       </c>
       <c r="E16" s="38">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>28</v>
@@ -2500,7 +2083,7 @@
         <v>34</v>
       </c>
       <c r="E17" s="38">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>28</v>
@@ -2516,7 +2099,7 @@
         <v>35</v>
       </c>
       <c r="E18" s="38">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>28</v>
@@ -2532,7 +2115,7 @@
         <v>36</v>
       </c>
       <c r="E19" s="38">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>28</v>
@@ -2548,7 +2131,7 @@
         <v>37</v>
       </c>
       <c r="E20" s="38">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>28</v>
@@ -2564,7 +2147,7 @@
         <v>38</v>
       </c>
       <c r="E21" s="38">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>28</v>
@@ -2580,7 +2163,7 @@
         <v>39</v>
       </c>
       <c r="E22" s="38">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>28</v>
@@ -2596,7 +2179,7 @@
         <v>40</v>
       </c>
       <c r="E23" s="38">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>28</v>
@@ -2612,7 +2195,7 @@
         <v>41</v>
       </c>
       <c r="E24" s="38">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>28</v>
@@ -2628,7 +2211,7 @@
         <v>42</v>
       </c>
       <c r="E25" s="38">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>28</v>
@@ -2644,7 +2227,7 @@
         <v>43</v>
       </c>
       <c r="E26" s="38">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>28</v>
@@ -2660,7 +2243,7 @@
         <v>44</v>
       </c>
       <c r="E27" s="38">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>28</v>
@@ -2676,7 +2259,7 @@
         <v>45</v>
       </c>
       <c r="E28" s="38">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="F28" s="38" t="s">
         <v>28</v>
@@ -2692,7 +2275,7 @@
         <v>46</v>
       </c>
       <c r="E29" s="38">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>28</v>
@@ -2708,7 +2291,7 @@
         <v>47</v>
       </c>
       <c r="E30" s="38">
-        <v>116</v>
+        <v>6</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>28</v>
@@ -2724,7 +2307,7 @@
         <v>48</v>
       </c>
       <c r="E31" s="38">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>28</v>
@@ -2740,7 +2323,7 @@
         <v>49</v>
       </c>
       <c r="E32" s="38">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>28</v>
@@ -2756,7 +2339,7 @@
         <v>50</v>
       </c>
       <c r="E33" s="38">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="F33" s="38" t="s">
         <v>28</v>
@@ -2772,7 +2355,7 @@
         <v>51</v>
       </c>
       <c r="E34" s="38">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="F34" s="38" t="s">
         <v>28</v>
@@ -2788,7 +2371,7 @@
         <v>52</v>
       </c>
       <c r="E35" s="38">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F35" s="38" t="s">
         <v>28</v>
@@ -2804,7 +2387,7 @@
         <v>53</v>
       </c>
       <c r="E36" s="38">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="F36" s="38" t="s">
         <v>28</v>
@@ -2820,7 +2403,7 @@
         <v>54</v>
       </c>
       <c r="E37" s="38">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="F37" s="38" t="s">
         <v>28</v>
@@ -2836,7 +2419,7 @@
         <v>55</v>
       </c>
       <c r="E38" s="38">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F38" s="38" t="s">
         <v>28</v>
@@ -2852,7 +2435,7 @@
         <v>56</v>
       </c>
       <c r="E39" s="38">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="F39" s="38" t="s">
         <v>28</v>
@@ -2868,7 +2451,7 @@
         <v>57</v>
       </c>
       <c r="E40" s="38">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="F40" s="38" t="s">
         <v>28</v>
@@ -2884,7 +2467,7 @@
         <v>58</v>
       </c>
       <c r="E41" s="38">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="F41" s="38" t="s">
         <v>28</v>
@@ -2900,7 +2483,7 @@
         <v>59</v>
       </c>
       <c r="E42" s="38">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="F42" s="38" t="s">
         <v>28</v>
@@ -2916,7 +2499,7 @@
         <v>60</v>
       </c>
       <c r="E43" s="38">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="F43" s="38" t="s">
         <v>28</v>
@@ -2932,7 +2515,7 @@
         <v>61</v>
       </c>
       <c r="E44" s="38">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="F44" s="38" t="s">
         <v>28</v>
@@ -2948,7 +2531,7 @@
         <v>62</v>
       </c>
       <c r="E45" s="38">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="F45" s="38" t="s">
         <v>28</v>
@@ -2964,7 +2547,7 @@
         <v>63</v>
       </c>
       <c r="E46" s="38">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F46" s="38" t="s">
         <v>28</v>
@@ -2980,7 +2563,7 @@
         <v>64</v>
       </c>
       <c r="E47" s="38">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F47" s="38" t="s">
         <v>28</v>
@@ -2996,7 +2579,7 @@
         <v>65</v>
       </c>
       <c r="E48" s="38">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F48" s="38" t="s">
         <v>28</v>
@@ -3012,7 +2595,7 @@
         <v>66</v>
       </c>
       <c r="E49" s="38">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="F49" s="38" t="s">
         <v>28</v>
@@ -3028,7 +2611,7 @@
         <v>67</v>
       </c>
       <c r="E50" s="38">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F50" s="38" t="s">
         <v>28</v>
@@ -3044,7 +2627,7 @@
         <v>68</v>
       </c>
       <c r="E51" s="38">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="F51" s="38" t="s">
         <v>28</v>
@@ -3060,7 +2643,7 @@
         <v>69</v>
       </c>
       <c r="E52" s="38">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="F52" s="38" t="s">
         <v>28</v>
@@ -3076,7 +2659,7 @@
         <v>70</v>
       </c>
       <c r="E53" s="38">
-        <v>161</v>
+        <v>53</v>
       </c>
       <c r="F53" s="38" t="s">
         <v>28</v>
@@ -3092,7 +2675,7 @@
         <v>71</v>
       </c>
       <c r="E54" s="38">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F54" s="38" t="s">
         <v>28</v>
@@ -3108,7 +2691,7 @@
         <v>72</v>
       </c>
       <c r="E55" s="38">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="F55" s="38" t="s">
         <v>28</v>
@@ -3124,7 +2707,7 @@
         <v>73</v>
       </c>
       <c r="E56" s="38">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="F56" s="38" t="s">
         <v>28</v>
@@ -3140,7 +2723,7 @@
         <v>74</v>
       </c>
       <c r="E57" s="38">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="F57" s="38" t="s">
         <v>28</v>
@@ -3156,7 +2739,7 @@
         <v>75</v>
       </c>
       <c r="E58" s="38">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="F58" s="38" t="s">
         <v>28</v>
@@ -3172,7 +2755,7 @@
         <v>76</v>
       </c>
       <c r="E59" s="38">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="F59" s="38" t="s">
         <v>28</v>
@@ -3188,7 +2771,7 @@
         <v>77</v>
       </c>
       <c r="E60" s="38">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="F60" s="38" t="s">
         <v>28</v>
@@ -3204,7 +2787,7 @@
         <v>78</v>
       </c>
       <c r="E61" s="38">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="F61" s="38" t="s">
         <v>28</v>
@@ -3220,7 +2803,7 @@
         <v>79</v>
       </c>
       <c r="E62" s="38">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="F62" s="38" t="s">
         <v>28</v>
@@ -3236,7 +2819,7 @@
         <v>80</v>
       </c>
       <c r="E63" s="38">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="F63" s="38" t="s">
         <v>28</v>
@@ -3252,7 +2835,7 @@
         <v>81</v>
       </c>
       <c r="E64" s="38">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="F64" s="38" t="s">
         <v>28</v>
@@ -3268,7 +2851,7 @@
         <v>82</v>
       </c>
       <c r="E65" s="38">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="F65" s="38" t="s">
         <v>28</v>
@@ -3284,7 +2867,7 @@
         <v>83</v>
       </c>
       <c r="E66" s="38">
-        <v>85</v>
+        <v>194</v>
       </c>
       <c r="F66" s="38" t="s">
         <v>28</v>
@@ -3300,7 +2883,7 @@
         <v>84</v>
       </c>
       <c r="E67" s="38">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="F67" s="38" t="s">
         <v>28</v>
@@ -3316,7 +2899,7 @@
         <v>85</v>
       </c>
       <c r="E68" s="38">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="F68" s="38" t="s">
         <v>28</v>
@@ -3332,7 +2915,7 @@
         <v>86</v>
       </c>
       <c r="E69" s="38">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F69" s="38" t="s">
         <v>28</v>
@@ -3348,7 +2931,7 @@
         <v>87</v>
       </c>
       <c r="E70" s="38">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="F70" s="38" t="s">
         <v>28</v>
@@ -3364,7 +2947,7 @@
         <v>88</v>
       </c>
       <c r="E71" s="38">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F71" s="38" t="s">
         <v>28</v>
@@ -3380,7 +2963,7 @@
         <v>89</v>
       </c>
       <c r="E72" s="38">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="F72" s="38" t="s">
         <v>28</v>
@@ -3396,7 +2979,7 @@
         <v>90</v>
       </c>
       <c r="E73" s="38">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="F73" s="38" t="s">
         <v>28</v>
@@ -3412,7 +2995,7 @@
         <v>91</v>
       </c>
       <c r="E74" s="38">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="F74" s="38" t="s">
         <v>28</v>
@@ -3428,7 +3011,7 @@
         <v>92</v>
       </c>
       <c r="E75" s="38">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="F75" s="38" t="s">
         <v>28</v>
@@ -3444,7 +3027,7 @@
         <v>93</v>
       </c>
       <c r="E76" s="38">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F76" s="38" t="s">
         <v>28</v>
@@ -3460,7 +3043,7 @@
         <v>94</v>
       </c>
       <c r="E77" s="38">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="F77" s="38" t="s">
         <v>28</v>
@@ -3476,7 +3059,7 @@
         <v>95</v>
       </c>
       <c r="E78" s="38">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="F78" s="38" t="s">
         <v>28</v>
@@ -3492,7 +3075,7 @@
         <v>96</v>
       </c>
       <c r="E79" s="38">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F79" s="38" t="s">
         <v>28</v>
@@ -3508,7 +3091,7 @@
         <v>97</v>
       </c>
       <c r="E80" s="38">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F80" s="38" t="s">
         <v>28</v>
@@ -3524,7 +3107,7 @@
         <v>98</v>
       </c>
       <c r="E81" s="38">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F81" s="38" t="s">
         <v>28</v>
@@ -3540,7 +3123,7 @@
         <v>99</v>
       </c>
       <c r="E82" s="38">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F82" s="38" t="s">
         <v>28</v>
@@ -3556,7 +3139,7 @@
         <v>100</v>
       </c>
       <c r="E83" s="38">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="F83" s="38" t="s">
         <v>28</v>
@@ -3572,7 +3155,7 @@
         <v>101</v>
       </c>
       <c r="E84" s="38">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F84" s="38" t="s">
         <v>28</v>
@@ -3588,7 +3171,7 @@
         <v>102</v>
       </c>
       <c r="E85" s="38">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="F85" s="38" t="s">
         <v>28</v>
@@ -3604,7 +3187,7 @@
         <v>103</v>
       </c>
       <c r="E86" s="38">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="F86" s="38" t="s">
         <v>28</v>
@@ -3620,7 +3203,7 @@
         <v>104</v>
       </c>
       <c r="E87" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F87" s="38" t="s">
         <v>28</v>
@@ -3636,7 +3219,7 @@
         <v>105</v>
       </c>
       <c r="E88" s="38">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="F88" s="38" t="s">
         <v>28</v>
@@ -3652,7 +3235,7 @@
         <v>106</v>
       </c>
       <c r="E89" s="38">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="F89" s="38" t="s">
         <v>28</v>
@@ -3668,7 +3251,7 @@
         <v>107</v>
       </c>
       <c r="E90" s="38">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F90" s="38" t="s">
         <v>28</v>
@@ -3684,7 +3267,7 @@
         <v>108</v>
       </c>
       <c r="E91" s="38">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="F91" s="38" t="s">
         <v>28</v>
@@ -3700,7 +3283,7 @@
         <v>109</v>
       </c>
       <c r="E92" s="38">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="F92" s="38" t="s">
         <v>28</v>
@@ -3716,7 +3299,7 @@
         <v>110</v>
       </c>
       <c r="E93" s="38">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F93" s="38" t="s">
         <v>28</v>
@@ -3732,7 +3315,7 @@
         <v>111</v>
       </c>
       <c r="E94" s="38">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="F94" s="38" t="s">
         <v>28</v>
@@ -3748,7 +3331,7 @@
         <v>112</v>
       </c>
       <c r="E95" s="38">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="F95" s="38" t="s">
         <v>28</v>
@@ -3764,7 +3347,7 @@
         <v>113</v>
       </c>
       <c r="E96" s="38">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F96" s="38" t="s">
         <v>28</v>
@@ -3780,7 +3363,7 @@
         <v>114</v>
       </c>
       <c r="E97" s="38">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="F97" s="38" t="s">
         <v>28</v>
@@ -3796,7 +3379,7 @@
         <v>115</v>
       </c>
       <c r="E98" s="38">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="F98" s="38" t="s">
         <v>28</v>
@@ -3812,7 +3395,7 @@
         <v>116</v>
       </c>
       <c r="E99" s="38">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F99" s="38" t="s">
         <v>28</v>
@@ -3828,7 +3411,7 @@
         <v>117</v>
       </c>
       <c r="E100" s="38">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="F100" s="38" t="s">
         <v>28</v>
@@ -3844,7 +3427,7 @@
         <v>118</v>
       </c>
       <c r="E101" s="38">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F101" s="38" t="s">
         <v>28</v>
@@ -3860,7 +3443,7 @@
         <v>119</v>
       </c>
       <c r="E102" s="38">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="F102" s="38" t="s">
         <v>28</v>
@@ -3876,7 +3459,7 @@
         <v>120</v>
       </c>
       <c r="E103" s="38">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="F103" s="38" t="s">
         <v>28</v>
@@ -3892,7 +3475,7 @@
         <v>121</v>
       </c>
       <c r="E104" s="38">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="F104" s="38" t="s">
         <v>28</v>
@@ -3908,7 +3491,7 @@
         <v>122</v>
       </c>
       <c r="E105" s="38">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="F105" s="38" t="s">
         <v>28</v>
@@ -3924,7 +3507,7 @@
         <v>123</v>
       </c>
       <c r="E106" s="38">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F106" s="38" t="s">
         <v>28</v>
@@ -3940,7 +3523,7 @@
         <v>124</v>
       </c>
       <c r="E107" s="38">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F107" s="38" t="s">
         <v>28</v>
@@ -3956,7 +3539,7 @@
         <v>125</v>
       </c>
       <c r="E108" s="38">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F108" s="38" t="s">
         <v>28</v>
@@ -3972,7 +3555,7 @@
         <v>126</v>
       </c>
       <c r="E109" s="38">
-        <v>175</v>
+        <v>55</v>
       </c>
       <c r="F109" s="38" t="s">
         <v>28</v>
@@ -3988,7 +3571,7 @@
         <v>127</v>
       </c>
       <c r="E110" s="38">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="F110" s="38" t="s">
         <v>28</v>
@@ -4004,7 +3587,7 @@
         <v>128</v>
       </c>
       <c r="E111" s="38">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="F111" s="38" t="s">
         <v>28</v>
@@ -4020,7 +3603,7 @@
         <v>129</v>
       </c>
       <c r="E112" s="38">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="F112" s="38" t="s">
         <v>28</v>
@@ -4036,7 +3619,7 @@
         <v>130</v>
       </c>
       <c r="E113" s="38">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="F113" s="38" t="s">
         <v>28</v>
@@ -4052,7 +3635,7 @@
         <v>131</v>
       </c>
       <c r="E114" s="38">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="F114" s="38" t="s">
         <v>28</v>
@@ -4068,7 +3651,7 @@
         <v>132</v>
       </c>
       <c r="E115" s="38">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="F115" s="38" t="s">
         <v>28</v>
@@ -4084,7 +3667,7 @@
         <v>133</v>
       </c>
       <c r="E116" s="38">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="F116" s="38" t="s">
         <v>28</v>
@@ -4116,7 +3699,7 @@
         <v>135</v>
       </c>
       <c r="E118" s="38">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F118" s="38" t="s">
         <v>28</v>
@@ -4132,7 +3715,7 @@
         <v>136</v>
       </c>
       <c r="E119" s="38">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="F119" s="38" t="s">
         <v>28</v>
@@ -4148,7 +3731,7 @@
         <v>137</v>
       </c>
       <c r="E120" s="38">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="F120" s="38" t="s">
         <v>28</v>
@@ -4164,7 +3747,7 @@
         <v>138</v>
       </c>
       <c r="E121" s="38">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F121" s="38" t="s">
         <v>28</v>
@@ -4180,7 +3763,7 @@
         <v>139</v>
       </c>
       <c r="E122" s="38">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="F122" s="38" t="s">
         <v>28</v>
@@ -4196,7 +3779,7 @@
         <v>140</v>
       </c>
       <c r="E123" s="38">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F123" s="38" t="s">
         <v>28</v>
@@ -4212,7 +3795,7 @@
         <v>141</v>
       </c>
       <c r="E124" s="38">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F124" s="38" t="s">
         <v>28</v>
@@ -4228,7 +3811,7 @@
         <v>142</v>
       </c>
       <c r="E125" s="38">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="F125" s="38" t="s">
         <v>28</v>
@@ -4244,7 +3827,7 @@
         <v>143</v>
       </c>
       <c r="E126" s="38">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F126" s="38" t="s">
         <v>28</v>
@@ -4260,7 +3843,7 @@
         <v>144</v>
       </c>
       <c r="E127" s="38">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F127" s="38" t="s">
         <v>28</v>
@@ -4276,7 +3859,7 @@
         <v>145</v>
       </c>
       <c r="E128" s="38">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="F128" s="38" t="s">
         <v>28</v>
@@ -4292,7 +3875,7 @@
         <v>146</v>
       </c>
       <c r="E129" s="38">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="F129" s="38" t="s">
         <v>28</v>
@@ -4308,7 +3891,7 @@
         <v>147</v>
       </c>
       <c r="E130" s="38">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="F130" s="38" t="s">
         <v>28</v>
@@ -4324,7 +3907,7 @@
         <v>148</v>
       </c>
       <c r="E131" s="38">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F131" s="38" t="s">
         <v>28</v>
@@ -4340,7 +3923,7 @@
         <v>149</v>
       </c>
       <c r="E132" s="38">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F132" s="38" t="s">
         <v>28</v>
@@ -4356,7 +3939,7 @@
         <v>150</v>
       </c>
       <c r="E133" s="38">
-        <v>55</v>
+        <v>161</v>
       </c>
       <c r="F133" s="38" t="s">
         <v>28</v>
@@ -4372,7 +3955,7 @@
         <v>151</v>
       </c>
       <c r="E134" s="38">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="F134" s="38" t="s">
         <v>28</v>
@@ -4422,7 +4005,7 @@
     </row>
     <row r="142">
       <c r="A142" s="26" t="s">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="B142" s="27"/>
       <c r="C142" s="27"/>
@@ -4445,19 +4028,19 @@
         <v>3</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>154</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145">
@@ -4465,19 +4048,19 @@
         <v>6</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>158</v>
+        <v>7</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>155</v>
+        <v>9</v>
       </c>
     </row>
     <row r="146">
@@ -4488,16 +4071,16 @@
         <v>11</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>156</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147">
@@ -4528,10 +4111,10 @@
       <c r="C148" s="33"/>
       <c r="D148" s="34"/>
       <c r="E148" s="11" t="s">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="F148" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="149">
@@ -4539,16 +4122,16 @@
         <v>22</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C149" s="14" t="s">
         <v>22</v>
       </c>
       <c r="D149" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E149" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F149" s="16" t="s">
         <v>23</v>
@@ -4559,7 +4142,7 @@
         <v>22</v>
       </c>
       <c r="B150" s="20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C150" s="21" t="s">
         <v>22</v>
@@ -4568,2382 +4151,68 @@
         <v>24</v>
       </c>
       <c r="E150" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F150" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="38" t="s">
+      <c r="A151" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B151" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C151" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="D151" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E151" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B152" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C152" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="D152" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E152" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B153" s="36"/>
+      <c r="C153" s="36"/>
+      <c r="D153" s="37"/>
+      <c r="E153" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="B151" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="C151" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D151" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E151" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="F151" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="B152" s="38"/>
-      <c r="C152" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D152" s="38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E152" s="38" t="s">
-        <v>165</v>
-      </c>
-      <c r="F152" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="B153" s="38"/>
-      <c r="C153" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D153" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="E153" s="38" t="s">
-        <v>167</v>
-      </c>
-      <c r="F153" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="B154" s="38"/>
-      <c r="C154" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D154" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="E154" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="F154" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="B155" s="38"/>
-      <c r="C155" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D155" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="E155" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="F155" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="B156" s="38"/>
-      <c r="C156" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D156" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="E156" s="38" t="s">
-        <v>173</v>
-      </c>
-      <c r="F156" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="B157" s="38"/>
-      <c r="C157" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D157" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="E157" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="F157" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="B158" s="38"/>
-      <c r="C158" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D158" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="E158" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="F158" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="B159" s="38"/>
-      <c r="C159" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D159" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="E159" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="F159" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="B160" s="38"/>
-      <c r="C160" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D160" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E160" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="F160" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="B161" s="38"/>
-      <c r="C161" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D161" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="E161" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="F161" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="B162" s="38"/>
-      <c r="C162" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D162" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="E162" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="F162" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="38" t="s">
-        <v>185</v>
-      </c>
-      <c r="B163" s="38"/>
-      <c r="C163" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D163" s="38" t="s">
-        <v>61</v>
-      </c>
-      <c r="E163" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="F163" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="B164" s="38"/>
-      <c r="C164" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D164" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="E164" s="38" t="s">
-        <v>188</v>
-      </c>
-      <c r="F164" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="B165" s="38"/>
-      <c r="C165" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D165" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="E165" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="F165" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="B166" s="38"/>
-      <c r="C166" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D166" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="E166" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="F166" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="B167" s="38"/>
-      <c r="C167" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D167" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="E167" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="F167" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="38" t="s">
-        <v>194</v>
-      </c>
-      <c r="B168" s="38"/>
-      <c r="C168" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D168" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="E168" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="F168" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="B169" s="38"/>
-      <c r="C169" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D169" s="38" t="s">
-        <v>93</v>
-      </c>
-      <c r="E169" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="F169" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="B170" s="38"/>
-      <c r="C170" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D170" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="E170" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="F170" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="B171" s="38"/>
-      <c r="C171" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D171" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="E171" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="F171" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="B172" s="38"/>
-      <c r="C172" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D172" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="E172" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="F172" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="B173" s="38"/>
-      <c r="C173" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D173" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="E173" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="F173" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="B174" s="38"/>
-      <c r="C174" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D174" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="E174" s="38" t="s">
-        <v>206</v>
-      </c>
-      <c r="F174" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="B175" s="38"/>
-      <c r="C175" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D175" s="38" t="s">
-        <v>77</v>
-      </c>
-      <c r="E175" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="F175" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="B176" s="38"/>
-      <c r="C176" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D176" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="E176" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="F176" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="B177" s="38"/>
-      <c r="C177" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D177" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="E177" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="F177" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="B178" s="38"/>
-      <c r="C178" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D178" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E178" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="F178" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="B179" s="38"/>
-      <c r="C179" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D179" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="E179" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="F179" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="B180" s="38"/>
-      <c r="C180" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D180" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="E180" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="F180" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="B181" s="38"/>
-      <c r="C181" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D181" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E181" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="F181" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="B182" s="38"/>
-      <c r="C182" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D182" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="E182" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="F182" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="B183" s="38"/>
-      <c r="C183" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D183" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="E183" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="F183" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="B184" s="38"/>
-      <c r="C184" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D184" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="E184" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="F184" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="B185" s="38"/>
-      <c r="C185" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D185" s="38" t="s">
-        <v>141</v>
-      </c>
-      <c r="E185" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="F185" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="38" t="s">
-        <v>226</v>
-      </c>
-      <c r="B186" s="38"/>
-      <c r="C186" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D186" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="E186" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="F186" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="B187" s="38"/>
-      <c r="C187" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D187" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="E187" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="F187" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="B188" s="38"/>
-      <c r="C188" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D188" s="38" t="s">
-        <v>126</v>
-      </c>
-      <c r="E188" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="F188" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="38" t="s">
-        <v>232</v>
-      </c>
-      <c r="B189" s="38"/>
-      <c r="C189" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D189" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="E189" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="F189" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="B190" s="38"/>
-      <c r="C190" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D190" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="E190" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="F190" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="B191" s="38"/>
-      <c r="C191" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D191" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="E191" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="F191" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="B192" s="38"/>
-      <c r="C192" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D192" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="E192" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="F192" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="B193" s="38"/>
-      <c r="C193" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D193" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="E193" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="F193" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="38" t="s">
-        <v>238</v>
-      </c>
-      <c r="B194" s="38"/>
-      <c r="C194" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D194" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="E194" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="F194" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="B195" s="38"/>
-      <c r="C195" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D195" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="E195" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="F195" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="B196" s="38"/>
-      <c r="C196" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D196" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="E196" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="F196" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="B197" s="38"/>
-      <c r="C197" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D197" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="E197" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="F197" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="B198" s="38"/>
-      <c r="C198" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D198" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="E198" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="F198" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="B199" s="38"/>
-      <c r="C199" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D199" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="E199" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="F199" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="B200" s="38"/>
-      <c r="C200" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D200" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="E200" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="F200" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="B201" s="38"/>
-      <c r="C201" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D201" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="E201" s="38" t="s">
-        <v>248</v>
-      </c>
-      <c r="F201" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="B202" s="38"/>
-      <c r="C202" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D202" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="E202" s="38" t="s">
-        <v>250</v>
-      </c>
-      <c r="F202" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="B203" s="38"/>
-      <c r="C203" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D203" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="E203" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="F203" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="B204" s="38"/>
-      <c r="C204" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D204" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="E204" s="38" t="s">
-        <v>252</v>
-      </c>
-      <c r="F204" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="B205" s="38"/>
-      <c r="C205" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D205" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="E205" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="F205" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="B206" s="38"/>
-      <c r="C206" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D206" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="E206" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="F206" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="38" t="s">
-        <v>254</v>
-      </c>
-      <c r="B207" s="38"/>
-      <c r="C207" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D207" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="E207" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="F207" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="B208" s="38"/>
-      <c r="C208" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D208" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="E208" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="F208" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="B209" s="38"/>
-      <c r="C209" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D209" s="38" t="s">
-        <v>34</v>
-      </c>
-      <c r="E209" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="F209" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="B210" s="38"/>
-      <c r="C210" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D210" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="E210" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="F210" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="B211" s="38"/>
-      <c r="C211" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D211" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="E211" s="38" t="s">
-        <v>260</v>
-      </c>
-      <c r="F211" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="B212" s="38"/>
-      <c r="C212" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D212" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="E212" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="F212" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="B213" s="38"/>
-      <c r="C213" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D213" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="E213" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="F213" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="38" t="s">
-        <v>262</v>
-      </c>
-      <c r="B214" s="38"/>
-      <c r="C214" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D214" s="38" t="s">
-        <v>53</v>
-      </c>
-      <c r="E214" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="F214" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="B215" s="38"/>
-      <c r="C215" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D215" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="E215" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="F215" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="38" t="s">
-        <v>265</v>
-      </c>
-      <c r="B216" s="38"/>
-      <c r="C216" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D216" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="E216" s="38" t="s">
-        <v>266</v>
-      </c>
-      <c r="F216" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="B217" s="38"/>
-      <c r="C217" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D217" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E217" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="F217" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="38" t="s">
-        <v>167</v>
-      </c>
-      <c r="B218" s="38"/>
-      <c r="C218" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D218" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="E218" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="F218" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="B219" s="38"/>
-      <c r="C219" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D219" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="E219" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="F219" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="B220" s="38"/>
-      <c r="C220" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D220" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="E220" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="F220" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="38" t="s">
-        <v>269</v>
-      </c>
-      <c r="B221" s="38"/>
-      <c r="C221" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D221" s="38" t="s">
-        <v>119</v>
-      </c>
-      <c r="E221" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="F221" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="B222" s="38"/>
-      <c r="C222" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D222" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="E222" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="F222" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="B223" s="38"/>
-      <c r="C223" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D223" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="E223" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="F223" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="B224" s="38"/>
-      <c r="C224" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D224" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="E224" s="38" t="s">
-        <v>270</v>
-      </c>
-      <c r="F224" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="B225" s="38"/>
-      <c r="C225" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D225" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="E225" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="F225" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="B226" s="38"/>
-      <c r="C226" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D226" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="E226" s="38" t="s">
-        <v>273</v>
-      </c>
-      <c r="F226" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="B227" s="38"/>
-      <c r="C227" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D227" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="E227" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="F227" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="B228" s="38"/>
-      <c r="C228" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D228" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="E228" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="F228" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="38" t="s">
-        <v>252</v>
-      </c>
-      <c r="B229" s="38"/>
-      <c r="C229" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D229" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="E229" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="F229" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="38" t="s">
-        <v>206</v>
-      </c>
-      <c r="B230" s="38"/>
-      <c r="C230" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D230" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="E230" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="F230" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="38" t="s">
-        <v>274</v>
-      </c>
-      <c r="B231" s="38"/>
-      <c r="C231" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D231" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="E231" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="F231" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="38" t="s">
-        <v>276</v>
-      </c>
-      <c r="B232" s="38"/>
-      <c r="C232" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D232" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="E232" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="F232" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="B233" s="38"/>
-      <c r="C233" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D233" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="E233" s="38" t="s">
-        <v>249</v>
-      </c>
-      <c r="F233" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="B234" s="38"/>
-      <c r="C234" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D234" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="E234" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="F234" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="B235" s="38"/>
-      <c r="C235" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D235" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="E235" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="F235" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="B236" s="38"/>
-      <c r="C236" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D236" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="E236" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="F236" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="B237" s="38"/>
-      <c r="C237" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D237" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="E237" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="F237" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="B238" s="38"/>
-      <c r="C238" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D238" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="E238" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="F238" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="B239" s="38"/>
-      <c r="C239" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D239" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="E239" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="F239" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="B240" s="38"/>
-      <c r="C240" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D240" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="E240" s="38" t="s">
-        <v>254</v>
-      </c>
-      <c r="F240" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="38" t="s">
-        <v>260</v>
-      </c>
-      <c r="B241" s="38"/>
-      <c r="C241" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D241" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="E241" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="F241" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="B242" s="38"/>
-      <c r="C242" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D242" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="E242" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="F242" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="B243" s="38"/>
-      <c r="C243" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D243" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="E243" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="F243" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="B244" s="38"/>
-      <c r="C244" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D244" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="E244" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="F244" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="38" t="s">
-        <v>280</v>
-      </c>
-      <c r="B245" s="38"/>
-      <c r="C245" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D245" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="E245" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="F245" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="B246" s="38"/>
-      <c r="C246" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D246" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="E246" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="F246" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="B247" s="38"/>
-      <c r="C247" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D247" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="E247" s="38" t="s">
-        <v>262</v>
-      </c>
-      <c r="F247" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="38" t="s">
-        <v>281</v>
-      </c>
-      <c r="B248" s="38"/>
-      <c r="C248" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D248" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="E248" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="F248" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="38" t="s">
-        <v>282</v>
-      </c>
-      <c r="B249" s="38"/>
-      <c r="C249" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D249" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="E249" s="38" t="s">
-        <v>254</v>
-      </c>
-      <c r="F249" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="B250" s="38"/>
-      <c r="C250" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D250" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="E250" s="38" t="s">
-        <v>223</v>
-      </c>
-      <c r="F250" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="38" t="s">
-        <v>188</v>
-      </c>
-      <c r="B251" s="38"/>
-      <c r="C251" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D251" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="E251" s="38" t="s">
-        <v>282</v>
-      </c>
-      <c r="F251" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="B252" s="38"/>
-      <c r="C252" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D252" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="E252" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="F252" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="38" t="s">
-        <v>270</v>
-      </c>
-      <c r="B253" s="38"/>
-      <c r="C253" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D253" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="E253" s="38" t="s">
-        <v>270</v>
-      </c>
-      <c r="F253" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="B254" s="38"/>
-      <c r="C254" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D254" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="E254" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="F254" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="38" t="s">
-        <v>287</v>
-      </c>
-      <c r="B255" s="38"/>
-      <c r="C255" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D255" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="E255" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="F255" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="B256" s="38"/>
-      <c r="C256" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D256" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="E256" s="38" t="s">
-        <v>282</v>
-      </c>
-      <c r="F256" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="B257" s="38"/>
-      <c r="C257" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D257" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="E257" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="F257" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="B258" s="38"/>
-      <c r="C258" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D258" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="E258" s="38" t="s">
-        <v>235</v>
-      </c>
-      <c r="F258" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="38" t="s">
-        <v>289</v>
-      </c>
-      <c r="B259" s="38"/>
-      <c r="C259" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D259" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="E259" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="F259" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="B260" s="38"/>
-      <c r="C260" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D260" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="E260" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="F260" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="B261" s="38"/>
-      <c r="C261" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D261" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="E261" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="F261" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="38" t="s">
-        <v>290</v>
-      </c>
-      <c r="B262" s="38"/>
-      <c r="C262" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D262" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="E262" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="F262" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="38" t="s">
-        <v>291</v>
-      </c>
-      <c r="B263" s="38"/>
-      <c r="C263" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D263" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="E263" s="38" t="s">
-        <v>292</v>
-      </c>
-      <c r="F263" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="38" t="s">
-        <v>293</v>
-      </c>
-      <c r="B264" s="38"/>
-      <c r="C264" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D264" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E264" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="F264" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="38" t="s">
-        <v>250</v>
-      </c>
-      <c r="B265" s="38"/>
-      <c r="C265" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D265" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="E265" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="F265" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="B266" s="38"/>
-      <c r="C266" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D266" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="E266" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="F266" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="B267" s="38"/>
-      <c r="C267" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D267" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="E267" s="38" t="s">
-        <v>246</v>
-      </c>
-      <c r="F267" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="38" t="s">
-        <v>295</v>
-      </c>
-      <c r="B268" s="38"/>
-      <c r="C268" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D268" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="E268" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="F268" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="38" t="s">
-        <v>296</v>
-      </c>
-      <c r="B269" s="38"/>
-      <c r="C269" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D269" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="E269" s="38" t="s">
-        <v>294</v>
-      </c>
-      <c r="F269" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="38" t="s">
-        <v>297</v>
-      </c>
-      <c r="B270" s="38"/>
-      <c r="C270" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D270" s="38" t="s">
-        <v>146</v>
-      </c>
-      <c r="E270" s="38" t="s">
-        <v>287</v>
-      </c>
-      <c r="F270" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="38" t="s">
-        <v>298</v>
-      </c>
-      <c r="B271" s="38"/>
-      <c r="C271" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D271" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="E271" s="38" t="s">
-        <v>299</v>
-      </c>
-      <c r="F271" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="38" t="s">
-        <v>300</v>
-      </c>
-      <c r="B272" s="38"/>
-      <c r="C272" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D272" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="E272" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="F272" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="B273" s="38"/>
-      <c r="C273" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D273" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="E273" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="F273" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="B274" s="38"/>
-      <c r="C274" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="D274" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="E274" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="F274" s="38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B275" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="C275" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="D275" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="E275" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="F275" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B276" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="C276" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="D276" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="E276" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="F276" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B277" s="36"/>
-      <c r="C277" s="36"/>
-      <c r="D277" s="37"/>
-      <c r="E277" s="23" t="s">
-        <v>302</v>
-      </c>
-      <c r="F277" s="23" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="s">
-        <v>160</v>
-      </c>
-      <c r="B278" t="s">
-        <v>160</v>
-      </c>
-      <c r="C278" t="s">
-        <v>160</v>
-      </c>
-      <c r="D278" t="s">
-        <v>160</v>
-      </c>
-      <c r="E278" t="s">
-        <v>160</v>
-      </c>
-      <c r="F278" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="s">
-        <v>160</v>
-      </c>
-      <c r="B279" t="s">
-        <v>160</v>
-      </c>
-      <c r="C279" t="s">
-        <v>160</v>
-      </c>
-      <c r="D279" t="s">
-        <v>160</v>
-      </c>
-      <c r="E279" t="s">
-        <v>160</v>
-      </c>
-      <c r="F279" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="s">
-        <v>160</v>
-      </c>
-      <c r="B280" t="s">
-        <v>160</v>
-      </c>
-      <c r="C280" t="s">
-        <v>160</v>
-      </c>
-      <c r="D280" t="s">
-        <v>160</v>
-      </c>
-      <c r="E280" t="s">
-        <v>160</v>
-      </c>
-      <c r="F280" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="s">
-        <v>303</v>
-      </c>
-      <c r="B281" t="s">
-        <v>160</v>
-      </c>
-      <c r="C281" t="s">
-        <v>160</v>
-      </c>
-      <c r="D281" t="s">
-        <v>160</v>
-      </c>
-      <c r="E281" t="s">
-        <v>160</v>
-      </c>
-      <c r="F281" t="s">
-        <v>160</v>
+      <c r="F153" s="23" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
@@ -6954,8 +4223,7 @@
     <mergeCell ref="A142:F142"/>
     <mergeCell ref="A143:F143"/>
     <mergeCell ref="A148:D148"/>
-    <mergeCell ref="A277:D277"/>
-    <mergeCell ref="B151:B274"/>
+    <mergeCell ref="A153:D153"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D1">
     <cfRule type="duplicateValues" dxfId="12" priority="5"/>
